--- a/monitoring_forms/033_on_set_health_monitoring_service_request--monitoring_forms.xlsx
+++ b/monitoring_forms/033_on_set_health_monitoring_service_request--monitoring_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'monitoring_forms',_'name':_'monitoring_forms'}</t>
+          <t>monitoring_forms</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 'Monitoring Forms', 'name': 'Monitoring Forms'}</t>
+          <t>Monitoring Forms</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'production_request',_'name':_'production_request'}</t>
+          <t>production_request</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 'production_request', 'name': 'Production Request'}</t>
+          <t>Production Request</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'equipment_request',_'name':_'equipment_request'}</t>
+          <t>equipment_request</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 'equipment_request', 'name': 'Equipment Request'}</t>
+          <t>Equipment Request</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'los_angeles',_'name':_'los_angeles'}</t>
+          <t>los_angeles</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 'Los Angeles', 'name': 'Los Angeles'}</t>
+          <t>Los Angeles</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'new_york',_'name':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 'New York', 'name': 'New York'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'chicago',_'name':_'chicago'}</t>
+          <t>chicago</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 'Chicago', 'name': 'Chicago'}</t>
+          <t>Chicago</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'health',_'name':_'health'}</t>
+          <t>health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 'health', 'name': 'Health'}</t>
+          <t>Health</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'equipment',_'name':_'equipment'}</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 'equipment', 'name': 'Equipment'}</t>
+          <t>Equipment</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'dolly',_'name':_'dolly'}</t>
+          <t>dolly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 'dolly', 'name': 'Dolly'}</t>
+          <t>Dolly</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'grip',_'name':_'grip'}</t>
+          <t>grip</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 'grip', 'name': 'Grip'}</t>
+          <t>Grip</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'lighting',_'name':_'lighting'}</t>
+          <t>lighting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 'lighting', 'name': 'Lighting'}</t>
+          <t>Lighting</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_'less_than_10',_'name':_'less_than_10'}</t>
+          <t>less_than_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 'less_than_10', 'name': 'Less than 10'}</t>
+          <t>Less than 10</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_'10_to_20',_'name':_'10_to_20'}</t>
+          <t>10_to_20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': '10_to_20', 'name': '10 to 20'}</t>
+          <t>10 to 20</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_'more_than_20',_'name':_'more_than_20'}</t>
+          <t>more_than_20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 'more_than_20', 'name': 'More than 20'}</t>
+          <t>More than 20</t>
         </is>
       </c>
     </row>
